--- a/songs/TakeOnMe_v1/quelle/struktur.xlsx
+++ b/songs/TakeOnMe_v1/quelle/struktur.xlsx
@@ -436,15 +436,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="70" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -468,6 +469,7 @@
       <c r="C2" s="2" t="n">
         <v>3</v>
       </c>
+      <c r="D2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
@@ -478,6 +480,7 @@
       <c r="C3" s="2" t="n">
         <v>154</v>
       </c>
+      <c r="D3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
@@ -488,6 +491,7 @@
       <c r="C4" s="2" t="n">
         <v>0.375</v>
       </c>
+      <c r="D4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -502,20 +506,25 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Effektidee</t>
+          <t>Effekt (füllt KI)</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t>Änderungswunsch</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
           <t>Energie 0-5</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>BPM pro Part</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>bisher (alter Code)</t>
         </is>
@@ -530,13 +539,19 @@
           <t>pause</t>
         </is>
       </c>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progBlack(5650, 5)   (Matrix: progScrollText("Take on me by a-ha", 14000, 90, getRandomColor(), 10))</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>progBlack(5650, 5)   (Matrix: progScrollText("Take on me by a-ha", 14000, 90, getRandomColor(), 10))</t>
         </is>
@@ -551,13 +566,19 @@
           <t>drumIntro</t>
         </is>
       </c>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progPalette(6235, 8, 10)</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>progPalette(6235, 8, 10)</t>
         </is>
@@ -572,13 +593,19 @@
           <t>synthIntro</t>
         </is>
       </c>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progPalette(6230, 4, 15)</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>progPalette(6230, 4, 15)</t>
         </is>
@@ -593,13 +620,19 @@
           <t>gitIntro</t>
         </is>
       </c>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progPalette(6235, 6, 20)</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>progPalette(6235, 6, 20)</t>
         </is>
@@ -614,13 +647,19 @@
           <t>chorus 1</t>
         </is>
       </c>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progStrobo(18700, 25, 195, getRandomCRGB())</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>progStrobo(18700, 25, 195, getRandomCRGB())</t>
         </is>
@@ -635,13 +674,19 @@
           <t>verse 1</t>
         </is>
       </c>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progMatrixScanner(18705, 30, 24)</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>progMatrixScanner(18705, 30, 24)</t>
         </is>
@@ -656,13 +701,19 @@
           <t>take on me</t>
         </is>
       </c>
-      <c r="C12" s="6" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progWaterRipple(12465, 35, 50, true, true)</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>progWaterRipple(12465, 35, 50, true, true)</t>
         </is>
@@ -677,13 +728,19 @@
           <t>tom-halfTime</t>
         </is>
       </c>
-      <c r="C13" s="6" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progStrobo(6235, 40, 780, getRandomCRGB())</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>progStrobo(6235, 40, 780, getRandomCRGB())</t>
         </is>
@@ -698,13 +755,19 @@
           <t>letzter durchgang</t>
         </is>
       </c>
-      <c r="C14" s="6" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFastBlingBling(6235, 6, 45)</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(6235, 6, 45)</t>
         </is>
@@ -719,13 +782,19 @@
           <t>chorus 2</t>
         </is>
       </c>
-      <c r="C15" s="6" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progStrobo(12465, 50, 195, getRandomCRGB())</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t>progStrobo(12465, 50, 195, getRandomCRGB())</t>
         </is>
@@ -740,13 +809,19 @@
           <t>verse 2</t>
         </is>
       </c>
-      <c r="C16" s="6" t="n"/>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progRandomLines(18700, 55, 390, false)</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
         <is>
           <t>progRandomLines(18700, 55, 390, false)</t>
         </is>
@@ -761,13 +836,19 @@
           <t>take on me</t>
         </is>
       </c>
-      <c r="C17" s="6" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progWaterRipple(12470, 60, 50, true, false)</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
         <is>
           <t>progWaterRipple(12470, 60, 50, true, false)</t>
         </is>
@@ -782,13 +863,19 @@
           <t>tom-halfTime</t>
         </is>
       </c>
-      <c r="C18" s="6" t="n"/>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F18" s="6" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progStrobo(6235, 65, 780, getRandomCRGB())</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
         <is>
           <t>progStrobo(6235, 65, 780, getRandomCRGB())</t>
         </is>
@@ -803,13 +890,20 @@
           <t>letzter durchgang</t>
         </is>
       </c>
-      <c r="C19" s="6" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F19" s="6" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFastBlingBling(6230, 6, 70)
+! der alte Code setzt hier Marker: markerLED4 = ESaite_Fis</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(6230, 6, 70)
 ! der alte Code setzt hier Marker: markerLED4 = ESaite_Fis</t>
@@ -825,13 +919,20 @@
           <t>BRIDGE</t>
         </is>
       </c>
-      <c r="C20" s="6" t="n"/>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F20" s="6" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progPalette(18705, 9, 75)
+! der alte Code setzt hier Marker: markerLED1 = ESaite_F; markerLED2 = 0; markerLED3 = 0; markerLED4 = ESaite_Fis</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
         <is>
           <t>progPalette(18705, 9, 75)
 ! der alte Code setzt hier Marker: markerLED1 = ESaite_F; markerLED2 = 0; markerLED3 = 0; markerLED4 = ESaite_Fis</t>
@@ -847,13 +948,20 @@
           <t>SOLO SYNTH</t>
         </is>
       </c>
-      <c r="C21" s="6" t="n"/>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progBlack(6230, 80)
+! der alte Code setzt hier Marker: markerLED4 = 0</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
         <is>
           <t>progBlack(6230, 80)
 ! der alte Code setzt hier Marker: markerLED4 = 0</t>
@@ -869,13 +977,19 @@
           <t>chorus 3</t>
         </is>
       </c>
-      <c r="C22" s="6" t="n"/>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F22" s="6" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progStrobo(18705, 85, 195, getRandomCRGB())</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>progStrobo(18705, 85, 195, getRandomCRGB())</t>
         </is>
@@ -890,13 +1004,19 @@
           <t>verse 3</t>
         </is>
       </c>
-      <c r="C23" s="6" t="n"/>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F23" s="6" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progWaterRipple(18700, 90, 50, true, false)</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
         <is>
           <t>progWaterRipple(18700, 90, 50, true, false)</t>
         </is>
@@ -911,13 +1031,19 @@
           <t>take on me</t>
         </is>
       </c>
-      <c r="C24" s="6" t="n"/>
-      <c r="D24" s="5" t="n"/>
-      <c r="E24" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F24" s="6" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progWaterRipple(12465, 95, 50, true, false)</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
         <is>
           <t>progWaterRipple(12465, 95, 50, true, false)</t>
         </is>
@@ -932,13 +1058,19 @@
           <t>tom-halfTime</t>
         </is>
       </c>
-      <c r="C25" s="6" t="n"/>
-      <c r="D25" s="5" t="n"/>
-      <c r="E25" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F25" s="6" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progStrobo(6235, 100, 780, getRandomCRGB())</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
         <is>
           <t>progStrobo(6235, 100, 780, getRandomCRGB())</t>
         </is>
@@ -953,13 +1085,19 @@
           <t>letzter durchgang</t>
         </is>
       </c>
-      <c r="C26" s="6" t="n"/>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F26" s="6" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFastBlingBling(6235, 6, 105)</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(6235, 6, 105)</t>
         </is>
@@ -974,13 +1112,19 @@
           <t>chorus 3</t>
         </is>
       </c>
-      <c r="C27" s="6" t="n"/>
-      <c r="D27" s="5" t="n"/>
-      <c r="E27" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F27" s="6" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progStrobo(18700, 110, 195, getRandomCRGB())</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
         <is>
           <t>progStrobo(18700, 110, 195, getRandomCRGB())</t>
         </is>
@@ -1000,10 +1144,10 @@
           <t>10 sek. BLACK</t>
         </is>
       </c>
-      <c r="D28" t="n">
+      <c r="E28" t="n">
         <v>0</v>
       </c>
-      <c r="E28">
+      <c r="F28">
         <f>$C$3</f>
         <v/>
       </c>

--- a/songs/TakeOnMe_v1/quelle/struktur.xlsx
+++ b/songs/TakeOnMe_v1/quelle/struktur.xlsx
@@ -532,7 +532,7 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
@@ -559,7 +559,7 @@
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
@@ -613,7 +613,7 @@
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
@@ -640,7 +640,7 @@
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
@@ -667,7 +667,7 @@
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
@@ -694,7 +694,7 @@
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>

--- a/songs/TakeOnMe_v1/quelle/struktur.xlsx
+++ b/songs/TakeOnMe_v1/quelle/struktur.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\00_DATEN\PlatformIO\Projects\LED-GIT_on_YULC\songs\TakeOnMe_v1\quelle\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D71D9C5-C07A-479C-A2FF-DF80D5874F8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{620F14DC-6460-482F-B3D0-A80E8F3D7DA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-36" yWindow="888" windowWidth="31908" windowHeight="24192" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7536" yWindow="2820" windowWidth="38352" windowHeight="20436" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Struktur" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="93">
   <si>
     <t>Take On Me</t>
   </si>
@@ -394,12 +394,6 @@
   </si>
   <si>
     <t>10 sek. BLACK</t>
-  </si>
-  <si>
-    <t>das letzte take on me scheint noch zu fehlen …irgendwas ist hier noch nicht so wie oben ab 44 und 80!</t>
-  </si>
-  <si>
-    <t>die schwarz ausgestanzte rund um die schrift erkennt man nur beim letzten me …warum auch immer !?</t>
   </si>
 </sst>
 </file>
@@ -2838,9 +2832,7 @@
       <c r="C166" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D166" s="8" t="s">
-        <v>94</v>
-      </c>
+      <c r="D166" s="8"/>
       <c r="E166" s="6"/>
       <c r="F166" s="5"/>
       <c r="G166" s="5">
@@ -7398,9 +7390,7 @@
       <c r="C534" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="D534" s="8" t="s">
-        <v>93</v>
-      </c>
+      <c r="D534" s="8"/>
       <c r="E534" s="6"/>
       <c r="F534" s="5"/>
       <c r="G534" s="5">
